--- a/updates/members/hassaan-tayyab/info.xlsx
+++ b/updates/members/hassaan-tayyab/info.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Member" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="README" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Member" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -536,7 +536,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hassaantayyab3@gmail.com</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -568,7 +568,6 @@
           <t>Photo Filename</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Drop your photo in this same folder and enter just the filename here (e.g. me.jpg).</t>

--- a/updates/members/hassaan-tayyab/info.xlsx
+++ b/updates/members/hassaan-tayyab/info.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Member" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="README" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Member" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -519,7 +519,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MITACS GRI'26 Intern</t>
+          <t>Research Assistant (Jun 2026 - Pres)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hassaantayyab3@gmail.com</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -568,7 +568,11 @@
           <t>Photo Filename</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>hassaan-tayyab.jpg</t>
+        </is>
+      </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Drop your photo in this same folder and enter just the filename here (e.g. me.jpg).</t>
